--- a/data/fmsForecastOutput/File1/RPT_RPT6577630625872WM_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT6577630625872WM_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>434.5012923340345</v>
+        <v>434.5012921455905</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>467.218544502928</v>
+        <v>467.2185452862584</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>503.5452882218342</v>
+        <v>503.545287748574</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>568.7318702625362</v>
+        <v>568.731870723232</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>614.3758372863609</v>
+        <v>614.3758369935795</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>434.5012923340345</v>
+        <v>434.5012921455905</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>467.218544502928</v>
+        <v>467.2185452862584</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>503.5452882218342</v>
+        <v>503.545287748574</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>568.7318702625362</v>
+        <v>568.731870723232</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>614.3758372863609</v>
+        <v>614.3758369935795</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>7024521.214368416</v>
+        <v>7024521.211321868</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>8294787.456674268</v>
+        <v>8294787.470581162</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>9577994.062995151</v>
+        <v>9577994.053993212</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>11048121.26032949</v>
+        <v>11048121.26927892</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>12761392.30828083</v>
+        <v>12761392.30219938</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>540.4425767162879</v>
+        <v>540.442576481897</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>581.1370381073026</v>
+        <v>581.1370390816268</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>626.3210670746201</v>
+        <v>626.3210664859683</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>707.4016184722002</v>
+        <v>707.4016190452243</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>764.1746214186334</v>
+        <v>764.1746210544651</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>540.4425767162879</v>
+        <v>540.442576481897</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>581.1370381073026</v>
+        <v>581.1370390816268</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>626.3210670746201</v>
+        <v>626.3210664859683</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>707.4016184722002</v>
+        <v>707.4016190452243</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>764.1746214186334</v>
+        <v>764.1746210544651</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>7024521.214368416</v>
+        <v>7024521.211321868</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>8294787.456674268</v>
+        <v>8294787.470581162</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>9577994.062995151</v>
+        <v>9577994.053993212</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>11048121.26032949</v>
+        <v>11048121.26927892</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>12761392.30828083</v>
+        <v>12761392.30219938</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>851.2908448307485</v>
+        <v>851.2908446886333</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>935.337884406259</v>
+        <v>935.3378843459403</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1013.436084648412</v>
+        <v>1013.436085012413</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1278.882916874059</v>
+        <v>1278.882916690189</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1376.329761730897</v>
+        <v>1376.329762003195</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>851.2908448307485</v>
+        <v>851.2908446886333</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>935.337884406259</v>
+        <v>935.3378843459403</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>1013.436084648412</v>
+        <v>1013.436085012413</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1278.882916874059</v>
+        <v>1278.882916690189</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>1376.329761730897</v>
+        <v>1376.329762003195</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>2842420.62454359</v>
+        <v>2842420.624069074</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>3335182.545594497</v>
+        <v>3335182.545379415</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>3844631.69130844</v>
+        <v>3844631.692689336</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>4298566.9626527</v>
+        <v>4298566.962034678</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>4972032.84331815</v>
+        <v>4972032.844301837</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1034.571334524749</v>
+        <v>1034.571334352037</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1136.713461888727</v>
+        <v>1136.713461815421</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1231.625981786164</v>
+        <v>1231.625982228534</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1554.2227595251</v>
+        <v>1554.222759301643</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1672.649632010505</v>
+        <v>1672.649632341429</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>1034.571334524749</v>
+        <v>1034.571334352037</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>1136.713461888727</v>
+        <v>1136.713461815421</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1231.625981786164</v>
+        <v>1231.625982228534</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1554.2227595251</v>
+        <v>1554.222759301643</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1672.649632010505</v>
+        <v>1672.649632341429</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>2842420.62454359</v>
+        <v>2842420.624069074</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>3335182.545594497</v>
+        <v>3335182.545379415</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>3844631.69130844</v>
+        <v>3844631.692689336</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>4298566.9626527</v>
+        <v>4298566.962034678</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>4972032.84331815</v>
+        <v>4972032.844301837</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>505.8462287675477</v>
+        <v>505.8462285870341</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>545.5136672720287</v>
+        <v>545.5136679142548</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>588.3303456676983</v>
+        <v>588.3303453336587</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>673.482112801515</v>
+        <v>673.4821131671348</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>727.2613098641549</v>
+        <v>727.2613096550914</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>505.8462287675477</v>
+        <v>505.8462285870341</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>545.5136672720287</v>
+        <v>545.5136679142548</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>588.3303456676983</v>
+        <v>588.3303453336587</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>673.482112801515</v>
+        <v>673.4821131671348</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>727.2613098641549</v>
+        <v>727.2613096550914</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>9866941.838912006</v>
+        <v>9866941.835390942</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>11629970.00226876</v>
+        <v>11629970.01596058</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>13422625.75430359</v>
+        <v>13422625.74668255</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>15346688.22298219</v>
+        <v>15346688.2313136</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>17733425.15159899</v>
+        <v>17733425.14650122</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>626.6651569072087</v>
+        <v>626.6651566835806</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>675.8689530481857</v>
+        <v>675.8689538438776</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>728.9336493653519</v>
+        <v>728.9336489514809</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>834.8020712911305</v>
+        <v>834.8020717443276</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>901.4493891884772</v>
+        <v>901.4493889293406</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>626.6651569072087</v>
+        <v>626.6651566835806</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>675.8689530481857</v>
+        <v>675.8689538438776</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>728.9336493653519</v>
+        <v>728.9336489514809</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>834.8020712911305</v>
+        <v>834.8020717443276</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>901.4493891884772</v>
+        <v>901.4493889293406</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>9866941.838912006</v>
+        <v>9866941.835390942</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>11629970.00226876</v>
+        <v>11629970.01596058</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>13422625.75430359</v>
+        <v>13422625.74668255</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>15346688.22298219</v>
+        <v>15346688.2313136</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>17733425.15159899</v>
+        <v>17733425.14650122</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>1501.313134760603</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1594.757040027311</v>
+        <v>1594.757040027312</v>
       </c>
       <c r="Y11" s="155" t="n">
         <v>1174.044843550935</v>
@@ -2395,7 +2395,7 @@
         <v>1501.313134760603</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1594.757040027311</v>
+        <v>1594.757040027312</v>
       </c>
       <c r="AD11" s="158" t="n">
         <v>108159.2265587395</v>
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>508.9311622607819</v>
+        <v>508.9311620811367</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>548.9437354450226</v>
+        <v>548.9437360841599</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>592.1332142540558</v>
+        <v>592.1332139216782</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>677.8085434735668</v>
+        <v>677.808543837193</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>732.0817128956597</v>
+        <v>732.0817126878093</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>508.9311622607819</v>
+        <v>508.9311620811367</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>548.9437354450226</v>
+        <v>548.9437360841599</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>592.1332142540558</v>
+        <v>592.1332139216782</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>677.8085434735668</v>
+        <v>677.808543837193</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>732.0817128956597</v>
+        <v>732.0817126878093</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>9975101.065470746</v>
+        <v>9975101.061949681</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>11759654.84835853</v>
+        <v>11759654.86205035</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>13576938.80851953</v>
+        <v>13576938.80089849</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>15529957.41937382</v>
+        <v>15529957.42770522</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>17955124.21481148</v>
+        <v>17955124.20971371</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>629.8492582497104</v>
+        <v>629.8492580273827</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>679.4305935895305</v>
+        <v>679.4305943805942</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>732.8774459804082</v>
+        <v>732.8774455690274</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>839.1987030540013</v>
+        <v>839.1987035042089</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>906.3144222935807</v>
+        <v>906.3144220362626</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>629.8492582497104</v>
+        <v>629.8492580273827</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>679.4305935895305</v>
+        <v>679.4305943805942</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>732.8774459804082</v>
+        <v>732.8774455690274</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>839.1987030540013</v>
+        <v>839.1987035042089</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>906.3144222935807</v>
+        <v>906.3144220362626</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>9975101.065470746</v>
+        <v>9975101.061949681</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>11759654.84835853</v>
+        <v>11759654.86205035</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>13576938.80851953</v>
+        <v>13576938.80089849</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>15529957.41937382</v>
+        <v>15529957.42770522</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>17955124.21481148</v>
+        <v>17955124.20971371</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>508.9245629993325</v>
+        <v>508.924562819698</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>548.9368506657245</v>
+        <v>548.9368513048257</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>592.1258550614488</v>
+        <v>592.125854729089</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>677.7978044072397</v>
+        <v>677.7978047708456</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>732.0704110989991</v>
+        <v>732.0704108911596</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>508.9245629993325</v>
+        <v>508.924562819698</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>548.9368506657245</v>
+        <v>548.9368513048257</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>592.1258550614488</v>
+        <v>592.125854729089</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>677.7978044072397</v>
+        <v>677.7978047708456</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>732.0704110989991</v>
+        <v>732.0704108911596</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>9975574.19304413</v>
+        <v>9975574.189523065</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>11760174.08410642</v>
+        <v>11760174.09779823</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>13577511.10637094</v>
+        <v>13577511.09874989</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>15530576.82096943</v>
+        <v>15530576.82930084</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>17955800.73677213</v>
+        <v>17955800.73167436</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>629.8265078739059</v>
+        <v>629.8265076515969</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>679.4073003500268</v>
+        <v>679.4073011410286</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>732.8529987967056</v>
+        <v>732.8529983853559</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>839.1674519051855</v>
+        <v>839.1674523553585</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>906.2819542917886</v>
+        <v>906.2819540344892</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>629.8265078739059</v>
+        <v>629.8265076515969</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>679.4073003500268</v>
+        <v>679.4073011410286</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>732.8529987967056</v>
+        <v>732.8529983853559</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>839.1674519051855</v>
+        <v>839.1674523553585</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>906.2819542917886</v>
+        <v>906.2819540344892</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>9975574.19304413</v>
+        <v>9975574.189523065</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>11760174.08410642</v>
+        <v>11760174.09779823</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>13577511.10637094</v>
+        <v>13577511.09874989</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>15530576.82096943</v>
+        <v>15530576.82930084</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>17955800.73677213</v>
+        <v>17955800.73167436</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>442.6589645635427</v>
+        <v>442.6589644523371</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>486.741491284291</v>
+        <v>486.741492145097</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>527.9634496664526</v>
+        <v>527.9634489735056</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>605.4758252137315</v>
+        <v>605.4758259356163</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>654.1626756839159</v>
+        <v>654.1626749879592</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>442.6589645635427</v>
+        <v>442.6589644523371</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>486.741491284291</v>
+        <v>486.741492145097</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>527.9634496664526</v>
+        <v>527.9634489735056</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>605.4758252137315</v>
+        <v>605.4758259356163</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>654.1626756839159</v>
+        <v>654.1626749879592</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>7156405.152683588</v>
+        <v>7156405.150885742</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>8641389.054544605</v>
+        <v>8641389.069826968</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>10042454.77947152</v>
+        <v>10042454.76629089</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>11761905.19105505</v>
+        <v>11761905.2050783</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>13587817.14904278</v>
+        <v>13587817.13458685</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>550.5892747296347</v>
+        <v>550.5892745913145</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>605.4201227603705</v>
+        <v>605.4201238310607</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>656.6929309163014</v>
+        <v>656.6929300543982</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>753.1045842468218</v>
+        <v>753.1045851447185</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>813.6623947402338</v>
+        <v>813.6623938745871</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>550.5892747296347</v>
+        <v>550.5892745913145</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>605.4201227603705</v>
+        <v>605.4201238310607</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>656.6929309163014</v>
+        <v>656.6929300543982</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>753.1045842468218</v>
+        <v>753.1045851447185</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>813.6623947402338</v>
+        <v>813.6623938745871</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>7156405.152683588</v>
+        <v>7156405.150885742</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>8641389.054544605</v>
+        <v>8641389.069826968</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>10042454.77947152</v>
+        <v>10042454.76629089</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>11761905.19105505</v>
+        <v>11761905.2050783</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>13587817.14904278</v>
+        <v>13587817.13458685</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>865.5571447256531</v>
+        <v>865.5571447256527</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>971.4113214462789</v>
@@ -4525,7 +4525,7 @@
         <v>1474.840076678236</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>865.5571447256531</v>
+        <v>865.5571447256527</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>971.4113214462789</v>
@@ -4540,7 +4540,7 @@
         <v>1474.840076678236</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>2890055.137828251</v>
+        <v>2890055.13782825</v>
       </c>
       <c r="N36" s="159" t="n">
         <v>3463811.460964313</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1051.909128077476</v>
+        <v>1051.909128077475</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>1180.553406986231</v>
@@ -4575,7 +4575,7 @@
         <v>1792.368936662237</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>1051.909128077476</v>
+        <v>1051.909128077475</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>1180.553406986231</v>
@@ -4590,7 +4590,7 @@
         <v>1792.368936662237</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>2890055.137828251</v>
+        <v>2890055.13782825</v>
       </c>
       <c r="AE36" s="159" t="n">
         <v>3463811.460964313</v>
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>515.0495597710653</v>
+        <v>515.0495596788955</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>567.8047600286421</v>
+        <v>567.8047607454744</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>616.0525060548313</v>
+        <v>616.0525054771081</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>717.9317413858945</v>
+        <v>717.9317420012984</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>775.7481853493407</v>
+        <v>775.7481847564919</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>515.0495597710653</v>
+        <v>515.0495596788955</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>567.8047600286421</v>
+        <v>567.8047607454744</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>616.0525060548313</v>
+        <v>616.0525054771081</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>717.9317413858945</v>
+        <v>717.9317420012984</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>775.7481853493407</v>
+        <v>775.7481847564919</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>10046460.29051184</v>
+        <v>10046460.28871399</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>12105200.51550892</v>
+        <v>12105200.53079128</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>14055100.66693955</v>
+        <v>14055100.65375893</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>16359565.29654579</v>
+        <v>16359565.31056904</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>18915721.48111506</v>
+        <v>18915721.46665913</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>638.0666590622021</v>
+        <v>638.066658948018</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>703.4866983542801</v>
+        <v>703.4866992424057</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>763.2810456675953</v>
+        <v>763.2810449518038</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>889.8987714187807</v>
+        <v>889.898772181593</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>961.5494710943095</v>
+        <v>961.5494703594661</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>638.0666590622021</v>
+        <v>638.066658948018</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>703.4866983542801</v>
+        <v>703.4866992424057</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>763.2810456675953</v>
+        <v>763.2810449518038</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>889.8987714187807</v>
+        <v>889.898772181593</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>961.5494710943095</v>
+        <v>961.5494703594661</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>10046460.29051184</v>
+        <v>10046460.28871399</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>12105200.51550892</v>
+        <v>12105200.53079128</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>14055100.66693955</v>
+        <v>14055100.65375893</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>16359565.29654579</v>
+        <v>16359565.31056904</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>18915721.48111506</v>
+        <v>18915721.46665913</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4747,7 +4747,7 @@
         <v>110640.6185610631</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>135732.1912059642</v>
+        <v>135732.1912059643</v>
       </c>
       <c r="O38" s="159" t="n">
         <v>162468.3891748899</v>
@@ -4776,7 +4776,7 @@
         <v>1603.022386220927</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1706.659926992531</v>
+        <v>1706.659926992532</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>1200.979813204906</v>
@@ -4791,13 +4791,13 @@
         <v>1603.022386220927</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1706.659926992531</v>
+        <v>1706.659926992532</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>110640.6185610631</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>135732.1912059642</v>
+        <v>135732.1912059643</v>
       </c>
       <c r="AF38" s="159" t="n">
         <v>162468.3891748899</v>
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>518.2168217571406</v>
+        <v>518.2168216654142</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>571.4099105802555</v>
+        <v>571.4099112936402</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>620.0731242003769</v>
+        <v>620.0731236255281</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>722.5576903559569</v>
+        <v>722.5576909680051</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>780.9215932202129</v>
+        <v>780.9215926308034</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>518.2168217571406</v>
+        <v>518.2168216654142</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>571.4099105802555</v>
+        <v>571.4099112936402</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>620.0731242003769</v>
+        <v>620.0731236255281</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>722.5576903559569</v>
+        <v>722.5576909680051</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>780.9215932202129</v>
+        <v>780.9215926308034</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>10157100.9090729</v>
+        <v>10157100.90727505</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>12240932.70671488</v>
+        <v>12240932.72199724</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>14217569.05611444</v>
+        <v>14217569.04293382</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>16555250.40561356</v>
+        <v>16555250.41963681</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>19152976.99875182</v>
+        <v>19152976.98429589</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>641.3411184065149</v>
+        <v>641.3411182929949</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>707.2370985593764</v>
+        <v>707.2370994423363</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>767.4583972755956</v>
+        <v>767.4583965641109</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>894.6028822843551</v>
+        <v>894.6028830421355</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>966.7780114551691</v>
+        <v>966.7780107254823</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>641.3411184065149</v>
+        <v>641.3411182929949</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>707.2370985593764</v>
+        <v>707.2370994423363</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>767.4583972755956</v>
+        <v>767.4583965641109</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>894.6028822843551</v>
+        <v>894.6028830421355</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>966.7780114551691</v>
+        <v>966.7780107254823</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>10157100.9090729</v>
+        <v>10157100.90727505</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>12240932.70671488</v>
+        <v>12240932.72199724</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>14217569.05611444</v>
+        <v>14217569.04293382</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>16555250.40561356</v>
+        <v>16555250.41963681</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>19152976.99875182</v>
+        <v>19152976.98429589</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>518.2073207430676</v>
+        <v>518.2073206513467</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>571.4000031329563</v>
+        <v>571.4000038463005</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>620.0626700398205</v>
+        <v>620.0626694650032</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>722.543143447371</v>
+        <v>722.543144059385</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>780.9065120398272</v>
+        <v>780.906511450449</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>518.2073207430676</v>
+        <v>518.2073206513467</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>571.4000031329563</v>
+        <v>571.4000038463005</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>620.0626700398205</v>
+        <v>620.0626694650032</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>722.543143447371</v>
+        <v>722.543144059385</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>780.9065120398272</v>
+        <v>780.906511450449</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>10157528.15109824</v>
+        <v>10157528.14930039</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>12241414.47300014</v>
+        <v>12241414.48828251</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>14218105.35234608</v>
+        <v>14218105.33916545</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>16555839.69556788</v>
+        <v>16555839.70959113</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>19153624.4487536</v>
+        <v>19153624.43429767</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>641.3145108477058</v>
+        <v>641.3145107341953</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>707.20945966326</v>
+        <v>707.2094605461507</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>767.4293957885307</v>
+        <v>767.4293950770998</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>894.5657313076669</v>
+        <v>894.5657320653888</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>966.7396320364768</v>
+        <v>966.7396313068436</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>641.3145108477058</v>
+        <v>641.3145107341953</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>707.20945966326</v>
+        <v>707.2094605461507</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>767.4293957885307</v>
+        <v>767.4293950770998</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>894.5657313076669</v>
+        <v>894.5657320653888</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>966.7396320364768</v>
+        <v>966.7396313068436</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>10157528.15109824</v>
+        <v>10157528.14930039</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>12241414.47300014</v>
+        <v>12241414.48828251</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>14218105.35234608</v>
+        <v>14218105.33916545</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>16555839.69556788</v>
+        <v>16555839.70959113</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>19153624.4487536</v>
+        <v>19153624.43429767</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>2.255217678296857</v>
+        <v>2.255217639619117</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>2.514114543340694</v>
+        <v>2.514114528089772</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>2.458633531451136</v>
+        <v>2.458633606550003</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>3.385192135581946</v>
+        <v>3.385191997372236</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>5.28151138304025</v>
+        <v>5.281511648246934</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>2.255217678296857</v>
+        <v>2.255217639619117</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>2.514114543340694</v>
+        <v>2.514114528089772</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>2.458633531451136</v>
+        <v>2.458633606550003</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.385192135581946</v>
+        <v>3.385191997372236</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>5.28151138304025</v>
+        <v>5.281511648246934</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>36459.78666511337</v>
+        <v>36459.78603981579</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>44634.4564532028</v>
+        <v>44634.45618244481</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>46765.95714057301</v>
+        <v>46765.95856903736</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>65760.36118067133</v>
+        <v>65760.35849582507</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>109703.9216863156</v>
+        <v>109703.9271950064</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>2.805090973533586</v>
+        <v>2.805090925425334</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>3.127112774887616</v>
+        <v>3.127112755918173</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>3.058104232097441</v>
+        <v>3.058104325507117</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>4.210578869871672</v>
+        <v>4.210578697963296</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>6.569263823068949</v>
+        <v>6.569264152939047</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>2.805090973533586</v>
+        <v>2.805090925425334</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>3.127112774887616</v>
+        <v>3.127112755918173</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>3.058104232097441</v>
+        <v>3.058104325507117</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>4.210578869871672</v>
+        <v>4.210578697963296</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>6.569263823068949</v>
+        <v>6.569264152939047</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>36459.78666511337</v>
+        <v>36459.78603981579</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>44634.4564532028</v>
+        <v>44634.45618244481</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>46765.95714057301</v>
+        <v>46765.95856903736</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>65760.36118067133</v>
+        <v>65760.35849582507</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>109703.9216863156</v>
+        <v>109703.9271950064</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>1.259339928817042</v>
+        <v>1.259339912335825</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>1.31526875599052</v>
+        <v>1.315268750254034</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>1.2883724618976</v>
+        <v>1.288372490438962</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>2.015404560527343</v>
+        <v>2.015404495667101</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>3.112149290527622</v>
+        <v>3.112149410623184</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>1.259339928817042</v>
+        <v>1.259339912335825</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>1.31526875599052</v>
+        <v>1.315268750254034</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>1.2883724618976</v>
+        <v>1.288372490438962</v>
       </c>
       <c r="K58" s="156" t="n">
-        <v>2.015404560527343</v>
+        <v>2.015404495667101</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>3.112149290527622</v>
+        <v>3.112149410623184</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>4204.877579404131</v>
+        <v>4204.877524374115</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>4689.921653852358</v>
+        <v>4689.921633397476</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>4887.646761600193</v>
+        <v>4887.646869876408</v>
       </c>
       <c r="P58" s="159" t="n">
-        <v>6774.155277199281</v>
+        <v>6774.155059191762</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>11242.73333038487</v>
+        <v>11242.73376423372</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>1.530472221906233</v>
+        <v>1.530472201876657</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>1.598442365974648</v>
+        <v>1.598442359003114</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>1.56575537651335</v>
+        <v>1.565755411199586</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>2.449315411358134</v>
+        <v>2.449315332533668</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>3.782186152115326</v>
+        <v>3.782186298067119</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>1.530472221906233</v>
+        <v>1.530472201876657</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>1.598442365974648</v>
+        <v>1.598442359003114</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>1.56575537651335</v>
+        <v>1.565755411199586</v>
       </c>
       <c r="AB58" s="156" t="n">
-        <v>2.449315411358134</v>
+        <v>2.449315332533668</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>3.782186152115326</v>
+        <v>3.782186298067119</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>4204.877579404131</v>
+        <v>4204.877524374115</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>4689.921653852358</v>
+        <v>4689.921633397476</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>4887.646761600193</v>
+        <v>4887.646869876408</v>
       </c>
       <c r="AG58" s="159" t="n">
-        <v>6774.155277199281</v>
+        <v>6774.155059191762</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>11242.73333038487</v>
+        <v>11242.73376423372</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>2.084745951482765</v>
+        <v>2.084745916604568</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>2.313602045563558</v>
+        <v>2.313602031903969</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>2.264041566457623</v>
+        <v>2.26404163381487</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>3.183142752709824</v>
+        <v>3.183142625319467</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>4.960114698609281</v>
+        <v>4.960114942317372</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>2.084745951482765</v>
+        <v>2.084745916604568</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>2.313602045563558</v>
+        <v>2.313602031903969</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>2.264041566457623</v>
+        <v>2.26404163381487</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>3.183142752709824</v>
+        <v>3.183142625319467</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>4.960114698609281</v>
+        <v>4.960114942317372</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>40664.6642445175</v>
+        <v>40664.6635641899</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>49324.37810705516</v>
+        <v>49324.37781584229</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>51653.6039021732</v>
+        <v>51653.60543891377</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>72534.51645787062</v>
+        <v>72534.51355501683</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>120946.6550167005</v>
+        <v>120946.6609592402</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>2.582677451170571</v>
+        <v>2.582677407961884</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>2.866457590558266</v>
+        <v>2.866457573634599</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>2.805118065905354</v>
+        <v>2.805118149360107</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>3.945604660714509</v>
+        <v>3.94560450281019</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>6.148123521380942</v>
+        <v>6.148123823460136</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>2.582677451170571</v>
+        <v>2.582677407961884</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>2.866457590558266</v>
+        <v>2.866457573634599</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>2.805118065905354</v>
+        <v>2.805118149360107</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.945604660714509</v>
+        <v>3.94560450281019</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>6.148123521380942</v>
+        <v>6.148123823460136</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>40664.6642445175</v>
+        <v>40664.6635641899</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>49324.37810705516</v>
+        <v>49324.37781584229</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>51653.6039021732</v>
+        <v>51653.60543891377</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>72534.51645787062</v>
+        <v>72534.51355501683</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>120946.6550167005</v>
+        <v>120946.6609592402</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>0.9062285887663047</v>
+        <v>0.9062285887663045</v>
       </c>
       <c r="D60" s="156" t="n">
         <v>0.6604342136030339</v>
@@ -6649,13 +6649,13 @@
         <v>0.6381275922591119</v>
       </c>
       <c r="F60" s="156" t="n">
-        <v>0.8435823535159963</v>
+        <v>0.8435823535159971</v>
       </c>
       <c r="G60" s="157" t="n">
-        <v>1.25606057317434</v>
+        <v>1.256060573174341</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.9062285887663047</v>
+        <v>0.9062285887663045</v>
       </c>
       <c r="I60" s="156" t="n">
         <v>0.6604342136030339</v>
@@ -6664,13 +6664,13 @@
         <v>0.6381275922591119</v>
       </c>
       <c r="K60" s="156" t="n">
-        <v>0.8435823535159963</v>
+        <v>0.8435823535159971</v>
       </c>
       <c r="L60" s="157" t="n">
-        <v>1.25606057317434</v>
+        <v>1.256060573174341</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>85.44468261825489</v>
+        <v>85.44468261825486</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>68.04515979529717</v>
@@ -6679,10 +6679,10 @@
         <v>72.79856307770591</v>
       </c>
       <c r="P60" s="159" t="n">
-        <v>105.3935595027948</v>
+        <v>105.3935595027949</v>
       </c>
       <c r="Q60" s="160" t="n">
-        <v>178.7097751091651</v>
+        <v>178.7097751091652</v>
       </c>
       <c r="S60" s="32" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>0.9274834170742566</v>
+        <v>0.9274834170742563</v>
       </c>
       <c r="U60" s="156" t="n">
         <v>0.6759241418538514</v>
@@ -6699,13 +6699,13 @@
         <v>0.6530943374933341</v>
       </c>
       <c r="W60" s="156" t="n">
-        <v>0.8633678671379067</v>
+        <v>0.8633678671379075</v>
       </c>
       <c r="X60" s="157" t="n">
         <v>1.285520416041969</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>0.9274834170742566</v>
+        <v>0.9274834170742563</v>
       </c>
       <c r="Z60" s="156" t="n">
         <v>0.6759241418538514</v>
@@ -6714,13 +6714,13 @@
         <v>0.6530943374933341</v>
       </c>
       <c r="AB60" s="156" t="n">
-        <v>0.8633678671379067</v>
+        <v>0.8633678671379075</v>
       </c>
       <c r="AC60" s="157" t="n">
         <v>1.285520416041969</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>85.44468261825489</v>
+        <v>85.44468261825486</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>68.04515979529717</v>
@@ -6729,10 +6729,10 @@
         <v>72.79856307770591</v>
       </c>
       <c r="AG60" s="159" t="n">
-        <v>105.3935595027948</v>
+        <v>105.3935595027949</v>
       </c>
       <c r="AH60" s="160" t="n">
-        <v>178.7097751091651</v>
+        <v>178.7097751091652</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" thickTop="1">
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>2.079076709340784</v>
+        <v>2.079076674630367</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>2.305651116501195</v>
+        <v>2.305651102907302</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>2.255951903850983</v>
+        <v>2.255951970873097</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>3.170385486408634</v>
+        <v>3.170385359712917</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>4.938627183584242</v>
+        <v>4.938627425878563</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>2.079076709340784</v>
+        <v>2.079076674630367</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>2.305651116501195</v>
+        <v>2.305651102907302</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>2.255951903850983</v>
+        <v>2.255951970873097</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>3.170385486408634</v>
+        <v>3.170385359712917</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>4.938627183584242</v>
+        <v>4.938627425878563</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>40750.10892713576</v>
+        <v>40750.10824680816</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>49392.42326685046</v>
+        <v>49392.42297563759</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>51726.4024652509</v>
+        <v>51726.40400199148</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>72639.91001737342</v>
+        <v>72639.90711451964</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>121125.3647918096</v>
+        <v>121125.3707343493</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>2.573049206508476</v>
+        <v>2.573049163551134</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>2.85371670272328</v>
+        <v>2.853716685898047</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>2.792169447261542</v>
+        <v>2.792169530214152</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>3.925272724862181</v>
+        <v>3.925272567999476</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>6.114001980884698</v>
+        <v>6.114002280844161</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>2.573049206508476</v>
+        <v>2.573049163551134</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>2.85371670272328</v>
+        <v>2.853716685898047</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>2.792169447261542</v>
+        <v>2.792169530214152</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>3.925272724862181</v>
+        <v>3.925272567999476</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>6.114001980884698</v>
+        <v>6.114002280844161</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>40750.10892713576</v>
+        <v>40750.10824680816</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>49392.42326685046</v>
+        <v>49392.42297563759</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>51726.4024652509</v>
+        <v>51726.40400199148</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>72639.91001737342</v>
+        <v>72639.90711451964</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>121125.3647918096</v>
+        <v>121125.3707343493</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>2.078951143722501</v>
+        <v>2.07895110901418</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>2.305520401394086</v>
+        <v>2.305520387800964</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>2.255828778119547</v>
+        <v>2.255828845138002</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>3.170208813856656</v>
+        <v>3.170208687167998</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>4.938364871473658</v>
+        <v>4.938365113755109</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>2.078951143722501</v>
+        <v>2.07895110901418</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>2.305520401394086</v>
+        <v>2.305520387800964</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>2.255828778119547</v>
+        <v>2.255828845138002</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>3.170208813856656</v>
+        <v>3.170208687167998</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>4.938364871473658</v>
+        <v>4.938365113755109</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>40750.10892713576</v>
+        <v>40750.10824680816</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>49392.42326685046</v>
+        <v>49392.42297563759</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>51726.4024652509</v>
+        <v>51726.40400199148</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>72639.91001737342</v>
+        <v>72639.90711451964</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>121125.3647918096</v>
+        <v>121125.3707343493</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>2.572834235342111</v>
+        <v>2.572834192388358</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>2.853492874295879</v>
+        <v>2.853492857471965</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>2.791958619414205</v>
+        <v>2.791958702360551</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>3.924970005853024</v>
+        <v>3.924969849002416</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>6.113552602141473</v>
+        <v>6.113552902078888</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>2.572834235342111</v>
+        <v>2.572834192388358</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>2.853492874295879</v>
+        <v>2.853492857471965</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>2.791958619414205</v>
+        <v>2.791958702360551</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>3.924970005853024</v>
+        <v>3.924969849002416</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>6.113552602141473</v>
+        <v>6.113552902078888</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>40750.10892713576</v>
+        <v>40750.10824680816</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>49392.42326685046</v>
+        <v>49392.42297563759</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>51726.4024652509</v>
+        <v>51726.40400199148</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>72639.91001737342</v>
+        <v>72639.90711451964</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>121125.3647918096</v>
+        <v>121125.3707343493</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>2.570444832767814</v>
+        <v>2.570444788683822</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>3.13234176247933</v>
+        <v>3.132341743478166</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>3.626829216371663</v>
+        <v>3.626829327153021</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.897188481257044</v>
+        <v>1.897188403799146</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>1.866699501642274</v>
+        <v>1.86669959537703</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>2.570444832767814</v>
+        <v>2.570444788683822</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>3.13234176247933</v>
+        <v>3.132341743478166</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>3.626829216371663</v>
+        <v>3.626829327153021</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>1.897188481257044</v>
+        <v>1.897188403799146</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>1.866699501642274</v>
+        <v>1.86669959537703</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>41556.01968672636</v>
+        <v>41556.01897402667</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>55610.18385747675</v>
+        <v>55610.18352013866</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>68986.34445488369</v>
+        <v>68986.34656206891</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>36854.56977283954</v>
+        <v>36854.56826815113</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>38773.79808318549</v>
+        <v>38773.80003017937</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>3.197177668369597</v>
+        <v>3.197177613536927</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>3.89607783253483</v>
+        <v>3.896077808900752</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>4.51113255952975</v>
+        <v>4.511132697322119</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>2.359766125940022</v>
+        <v>2.359766029596129</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>2.32184324056506</v>
+        <v>2.321843357154479</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>3.197177668369597</v>
+        <v>3.197177613536927</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>3.89607783253483</v>
+        <v>3.896077808900752</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>4.51113255952975</v>
+        <v>4.511132697322119</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>2.359766125940022</v>
+        <v>2.359766029596129</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>2.32184324056506</v>
+        <v>2.321843357154479</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>41556.01968672636</v>
+        <v>41556.01897402667</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>55610.18385747675</v>
+        <v>55610.18352013866</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>68986.34445488369</v>
+        <v>68986.34656206891</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>36854.56977283954</v>
+        <v>36854.56826815113</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>38773.79808318549</v>
+        <v>38773.80003017937</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>10.12702472861161</v>
+        <v>10.12702459607735</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>13.20830833490282</v>
+        <v>13.20830827729537</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>16.00574326845877</v>
+        <v>16.00574362303458</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.923670491238404</v>
+        <v>3.923670364965882</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>4.193907547327489</v>
+        <v>4.193907709167309</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>10.12702472861161</v>
+        <v>10.12702459607735</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>13.20830833490282</v>
+        <v>13.20830827729537</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>16.00574326845877</v>
+        <v>16.00574362303458</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>3.923670491238404</v>
+        <v>3.923670364965882</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>4.193907547327489</v>
+        <v>4.193907709167309</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>33813.66559814419</v>
+        <v>33813.66515561845</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>47097.54640523508</v>
+        <v>47097.54619982124</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>60720.34412926187</v>
+        <v>60720.34547440185</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>13188.19738963924</v>
+        <v>13188.19696521345</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>15150.61771310387</v>
+        <v>15150.61829775511</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>12.30734425474514</v>
+        <v>12.30734409367663</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>16.05201942888462</v>
+        <v>16.05201935887446</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>19.45173412102434</v>
+        <v>19.45173455193931</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>4.76842555162561</v>
+        <v>4.768425398166974</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>5.096843874756654</v>
+        <v>5.096844071440126</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>12.30734425474514</v>
+        <v>12.30734409367663</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>16.05201942888462</v>
+        <v>16.05201935887446</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>19.45173412102434</v>
+        <v>19.45173455193931</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>4.76842555162561</v>
+        <v>4.768425398166974</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>5.096843874756654</v>
+        <v>5.096844071440126</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>33813.66559814419</v>
+        <v>33813.66515561845</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>47097.54640523508</v>
+        <v>47097.54619982124</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>60720.34412926187</v>
+        <v>60720.34547440185</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>13188.19738963924</v>
+        <v>13188.19696521345</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>15150.61771310387</v>
+        <v>15150.61829775511</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>3.863960251026742</v>
+        <v>3.863960191802066</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>4.817593732560639</v>
+        <v>4.817593707102398</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>5.685205139959749</v>
+        <v>5.685205291279447</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>2.196103033392522</v>
+        <v>2.196102948734263</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>2.21148147807941</v>
+        <v>2.211481581904111</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>3.863960251026742</v>
+        <v>3.863960191802066</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>4.817593732560639</v>
+        <v>4.817593707102398</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>5.685205139959749</v>
+        <v>5.685205291279447</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>2.196103033392522</v>
+        <v>2.196102948734263</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>2.21148147807941</v>
+        <v>2.211481581904111</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>75369.68528487055</v>
+        <v>75369.68412964512</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>102707.7302627118</v>
+        <v>102707.7297199599</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>129706.6885841456</v>
+        <v>129706.6920364707</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>50042.76716247878</v>
+        <v>50042.76523336458</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>53924.41579628935</v>
+        <v>53924.41832793448</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>4.786848491274619</v>
+        <v>4.786848417904416</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>5.968800100866358</v>
+        <v>5.968800069324645</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>7.043895254728561</v>
+        <v>7.0438954422117</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.722138162539613</v>
+        <v>2.722138057603062</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>2.741158646248744</v>
+        <v>2.741158774940745</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>4.786848491274619</v>
+        <v>4.786848417904416</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>5.968800100866358</v>
+        <v>5.968800069324645</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>7.043895254728561</v>
+        <v>7.0438954422117</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>2.722138162539613</v>
+        <v>2.722138057603062</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>2.741158646248744</v>
+        <v>2.741158774940745</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>75369.68528487055</v>
+        <v>75369.68412964512</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>102707.7302627118</v>
+        <v>102707.7297199599</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>129706.6885841456</v>
+        <v>129706.6920364707</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>50042.76716247878</v>
+        <v>50042.76523336458</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>53924.41579628935</v>
+        <v>53924.41832793448</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>7.214822337435819</v>
+        <v>7.214822337435817</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>8.783529712855096</v>
@@ -7612,13 +7612,13 @@
         <v>10.17753349295958</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>8.713501568386055</v>
+        <v>8.713501568386066</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>9.320952109438554</v>
+        <v>9.320952109438556</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>7.214822337435819</v>
+        <v>7.214822337435817</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>8.783529712855096</v>
@@ -7627,13 +7627,13 @@
         <v>10.17753349295958</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>8.713501568386055</v>
+        <v>8.713501568386066</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>9.320952109438554</v>
+        <v>9.320952109438556</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>680.2568495532998</v>
+        <v>680.2568495532996</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>904.9753488955527</v>
@@ -7642,10 +7642,10 @@
         <v>1161.068449241788</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>1088.627497004627</v>
+        <v>1088.627497004628</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>1326.16634170067</v>
+        <v>1326.166341700671</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>7.38403991891086</v>
+        <v>7.384039918910858</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>8.989540004627816</v>
@@ -7662,13 +7662,13 @@
         <v>10.4162389693403</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>8.917869409009183</v>
+        <v>8.917869409009192</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>9.539567190896602</v>
+        <v>9.539567190896605</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>7.38403991891086</v>
+        <v>7.384039918910858</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>8.989540004627816</v>
@@ -7677,13 +7677,13 @@
         <v>10.4162389693403</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>8.917869409009183</v>
+        <v>8.917869409009192</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>9.539567190896602</v>
+        <v>9.539567190896605</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>680.2568495532998</v>
+        <v>680.2568495532996</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>904.9753488955527</v>
@@ -7692,10 +7692,10 @@
         <v>1161.068449241788</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>1088.627497004627</v>
+        <v>1088.627497004628</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>1326.16634170067</v>
+        <v>1326.166341700671</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>3.880079528648967</v>
+        <v>3.880079469709191</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>4.836667945738257</v>
+        <v>4.836667920402457</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>5.707556519719509</v>
+        <v>5.707556670286322</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.231641414333896</v>
+        <v>2.231641330137265</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>2.252724087349722</v>
+        <v>2.252724190572127</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>3.880079528648967</v>
+        <v>3.880079469709191</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>4.836667945738257</v>
+        <v>4.836667920402457</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>5.707556519719509</v>
+        <v>5.707556670286322</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>2.231641414333896</v>
+        <v>2.231641330137265</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>2.252724087349722</v>
+        <v>2.252724190572127</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>76049.94213442385</v>
+        <v>76049.94097919842</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>103612.7056116074</v>
+        <v>103612.7050688554</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>130867.7570333873</v>
+        <v>130867.7604857125</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>51131.39465948341</v>
+        <v>51131.39273036921</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>55250.58213799002</v>
+        <v>55250.58466963515</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>4.801956323942243</v>
+        <v>4.801956250998834</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>5.986369751909693</v>
+        <v>5.986369720551437</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>7.064186477413446</v>
+        <v>7.064186663768508</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.763008224996853</v>
+        <v>2.763008120752514</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>2.788863994071913</v>
+        <v>2.788864121860864</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>4.801956323942243</v>
+        <v>4.801956250998834</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>5.986369751909693</v>
+        <v>5.986369720551437</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>7.064186477413446</v>
+        <v>7.064186663768508</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.763008224996853</v>
+        <v>2.763008120752514</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>2.788863994071913</v>
+        <v>2.788864121860864</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>76049.94213442385</v>
+        <v>76049.94097919842</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>103612.7056116074</v>
+        <v>103612.7050688554</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>130867.7570333873</v>
+        <v>130867.7604857125</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>51131.39465948341</v>
+        <v>51131.39273036921</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>55250.58213799002</v>
+        <v>55250.58466963515</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>3.882982634009073</v>
+        <v>3.882982575072855</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>4.839458521581254</v>
+        <v>4.83945849624689</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>5.710324887417357</v>
+        <v>5.710325037975953</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>2.234801202731688</v>
+        <v>2.234801118539749</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>2.255873070631038</v>
+        <v>2.255873173847961</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>3.882982634009073</v>
+        <v>3.882982575072855</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>4.839458521581254</v>
+        <v>4.83945849624689</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>5.710324887417357</v>
+        <v>5.710325037975953</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>2.234801202731688</v>
+        <v>2.234801118539749</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>2.255873070631038</v>
+        <v>2.255873173847961</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>76111.44002870664</v>
+        <v>76111.43887348119</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>103678.3641280169</v>
+        <v>103678.363585265</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>130938.3789225849</v>
+        <v>130938.3823749101</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>51206.64530474928</v>
+        <v>51206.64337563508</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>55330.75333954934</v>
+        <v>55330.75587119447</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>4.805437918146158</v>
+        <v>4.805437845208841</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>5.98969343252501</v>
+        <v>5.989693401169214</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>7.067464935158057</v>
+        <v>7.067465121499048</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>2.766861176912605</v>
+        <v>2.766861072676305</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>2.792705488556127</v>
+        <v>2.792705616335686</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>4.805437918146158</v>
+        <v>4.805437845208841</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>5.98969343252501</v>
+        <v>5.989693401169214</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>7.067464935158057</v>
+        <v>7.067465121499048</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>2.766861176912605</v>
+        <v>2.766861072676305</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>2.792705488556127</v>
+        <v>2.792705616335686</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>76111.44002870664</v>
+        <v>76111.43887348119</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>103678.3641280169</v>
+        <v>103678.363585265</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>130938.3789225849</v>
+        <v>130938.3823749101</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>51206.64530474928</v>
+        <v>51206.64337563508</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>55330.75333954934</v>
+        <v>55330.75587119447</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>447.4846270746074</v>
+        <v>447.48462688064</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>492.387947590111</v>
+        <v>492.3879484166649</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>534.0489124142754</v>
+        <v>534.0489119072087</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>610.7582058305704</v>
+        <v>610.7582063367877</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>661.3108865685984</v>
+        <v>661.3108862315831</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>447.4846270746074</v>
+        <v>447.4846268806401</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>492.387947590111</v>
+        <v>492.3879484166649</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>534.0489124142754</v>
+        <v>534.0489119072085</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>610.7582058305704</v>
+        <v>610.7582063367878</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>661.3108865685984</v>
+        <v>661.3108862315833</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>7234420.959035427</v>
+        <v>7234420.955899585</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>8741633.694855284</v>
+        <v>8741633.709529551</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>10158207.08106697</v>
+        <v>10158207.071422</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>11864520.12200856</v>
+        <v>11864520.13184228</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>13736294.86881229</v>
+        <v>13736294.86181204</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>556.5915433715378</v>
+        <v>556.5915431302768</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>612.4433133677929</v>
+        <v>612.4433143958795</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>664.2621677079286</v>
+        <v>664.2621670772274</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>759.6749292426334</v>
+        <v>759.6749298722781</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>822.5535018038679</v>
+        <v>822.5535013846807</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>556.5915433715378</v>
+        <v>556.5915431302768</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>612.4433133677929</v>
+        <v>612.4433143958795</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>664.2621677079286</v>
+        <v>664.2621670772274</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>759.6749292426334</v>
+        <v>759.6749298722781</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>822.5535018038679</v>
+        <v>822.5535013846807</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>7234420.959035427</v>
+        <v>7234420.955899585</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>8741633.694855284</v>
+        <v>8741633.709529551</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>10158207.08106697</v>
+        <v>10158207.071422</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>11864520.12200856</v>
+        <v>11864520.13184228</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>13736294.86881229</v>
+        <v>13736294.86181204</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>876.9435093830816</v>
+        <v>876.9435092340659</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>985.9348985371721</v>
+        <v>985.9348984738283</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1075.018356642544</v>
+        <v>1075.018357025661</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1373.80632420518</v>
+        <v>1373.806324014048</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1482.146133516091</v>
+        <v>1482.146133798027</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>876.9435093830817</v>
+        <v>876.9435092340659</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>985.9348985371723</v>
+        <v>985.9348984738284</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1075.018356642544</v>
+        <v>1075.018357025661</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1373.80632420518</v>
+        <v>1373.806324014048</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1482.146133516092</v>
+        <v>1482.146133798027</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>2928073.681005799</v>
+        <v>2928073.680508242</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>3515598.929023401</v>
+        <v>3515598.928797532</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>4078253.8783589</v>
+        <v>4078253.879812316</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>4617622.458157581</v>
+        <v>4617622.457515148</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>5354297.683115767</v>
+        <v>5354297.684134267</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1065.746944554127</v>
+        <v>1065.746944373029</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1198.20386878109</v>
+        <v>1198.203868704108</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1306.466741212753</v>
+        <v>1306.466741678354</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1669.582905586249</v>
+        <v>1669.582905353966</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1801.247966689109</v>
+        <v>1801.247967031745</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>1065.746944554127</v>
+        <v>1065.746944373029</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1198.20386878109</v>
+        <v>1198.203868704108</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1306.466741212753</v>
+        <v>1306.466741678354</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1669.582905586249</v>
+        <v>1669.582905353966</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1801.247966689109</v>
+        <v>1801.247967031745</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>2928073.681005799</v>
+        <v>2928073.680508242</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>3515598.929023401</v>
+        <v>3515598.928797532</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>4078253.8783589</v>
+        <v>4078253.879812316</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>4617622.458157581</v>
+        <v>4617622.457515148</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>5354297.683115767</v>
+        <v>5354297.684134267</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>520.9982659735748</v>
+        <v>520.9982657873022</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>574.9359558067663</v>
+        <v>574.9359564844807</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>624.0017527612487</v>
+        <v>624.0017524022023</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>723.3109871719969</v>
+        <v>723.3109875753521</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>782.9197815260294</v>
+        <v>782.9197812807133</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>520.9982659735748</v>
+        <v>520.9982657873022</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>574.9359558067663</v>
+        <v>574.9359564844807</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>624.0017527612487</v>
+        <v>624.0017524022023</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>723.3109871719969</v>
+        <v>723.3109875753521</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>782.9197815260294</v>
+        <v>782.9197812807133</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>10162494.64004123</v>
+        <v>10162494.63640783</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>12257232.62387868</v>
+        <v>12257232.63832708</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>14236460.95942587</v>
+        <v>14236460.95123431</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>16482142.58016614</v>
+        <v>16482142.58935743</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>19090592.55192805</v>
+        <v>19090592.5459463</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>645.4361850046473</v>
+        <v>645.4361847738843</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>712.3219560457046</v>
+        <v>712.3219568853649</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>773.1300589882293</v>
+        <v>773.1300585433754</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>896.5665142420349</v>
+        <v>896.5665147420063</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>970.4387532619393</v>
+        <v>970.438752957867</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>645.4361850046473</v>
+        <v>645.4361847738843</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>712.3219560457046</v>
+        <v>712.3219568853649</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>773.1300589882293</v>
+        <v>773.1300585433754</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>896.5665142420349</v>
+        <v>896.5665147420063</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>970.4387532619393</v>
+        <v>970.438752957867</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>10162494.64004123</v>
+        <v>10162494.63640783</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>12257232.62387868</v>
+        <v>12257232.63832708</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>14236460.95942587</v>
+        <v>14236460.95123431</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>16482142.58016614</v>
+        <v>16482142.58935743</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>19090592.55192805</v>
+        <v>19090592.5459463</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8569,7 +8569,7 @@
         <v>1181.578410078496</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1326.836460753589</v>
+        <v>1326.83646075359</v>
       </c>
       <c r="E82" s="156" t="n">
         <v>1434.958633409061</v>
@@ -8608,7 +8608,7 @@
         <v>196879.1301242753</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>238760.393753569</v>
+        <v>238760.3937535691</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>196879.1301242753</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>238760.393753569</v>
+        <v>238760.3937535691</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>524.1759779951303</v>
+        <v>524.1759778097538</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>578.552229642495</v>
+        <v>578.55223031695</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>628.0366326239474</v>
+        <v>628.0366322666874</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>727.9597172566994</v>
+        <v>727.9597176578552</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>788.112944491147</v>
+        <v>788.1129442472541</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>524.1759779951303</v>
+        <v>524.1759778097538</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>578.552229642495</v>
+        <v>578.55223031695</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>628.0366326239474</v>
+        <v>628.0366322666874</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>727.9597172566994</v>
+        <v>727.9597176578552</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>788.112944491147</v>
+        <v>788.1129442472541</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>10273900.96013446</v>
+        <v>10273900.95650106</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>12393937.83559334</v>
+        <v>12393937.85004174</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>14400163.21561308</v>
+        <v>14400163.20742152</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>16679021.71029041</v>
+        <v>16679021.7194817</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>19329352.94568162</v>
+        <v>19329352.93969987</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>648.7161239369656</v>
+        <v>648.716123707545</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>716.0771850140093</v>
+        <v>716.0771858487858</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>777.3147532002707</v>
+        <v>777.3147527580935</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>901.2911632342141</v>
+        <v>901.2911637308875</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>975.6808774301259</v>
+        <v>975.6808771281874</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>648.7161239369656</v>
+        <v>648.716123707545</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>716.0771850140093</v>
+        <v>716.0771858487858</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>777.3147532002707</v>
+        <v>777.3147527580935</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>901.2911632342141</v>
+        <v>901.2911637308875</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>975.6808774301259</v>
+        <v>975.6808771281874</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>10273900.96013446</v>
+        <v>10273900.95650106</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>12393937.83559334</v>
+        <v>12393937.85004174</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>14400163.21561308</v>
+        <v>14400163.20742152</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>16679021.71029041</v>
+        <v>16679021.7194817</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>19329352.94568162</v>
+        <v>19329352.93969987</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>524.1692545207992</v>
+        <v>524.1692543354338</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>578.5449820559315</v>
+        <v>578.5449827303484</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>628.0288237053576</v>
+        <v>628.0288233481172</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>727.9481534639592</v>
+        <v>727.9481538650928</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>788.100749981932</v>
+        <v>788.1007497380521</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>524.1692545207992</v>
+        <v>524.1692543354338</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>578.5449820559315</v>
+        <v>578.5449827303484</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>628.0288237053576</v>
+        <v>628.0288233481172</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>727.9481534639592</v>
+        <v>727.9481538650928</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>788.100749981932</v>
+        <v>788.1007497380521</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>10274389.70005408</v>
+        <v>10274389.69642068</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>12394485.26039501</v>
+        <v>12394485.27484341</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>14400770.13373391</v>
+        <v>14400770.12554235</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>16679686.25088999</v>
+        <v>16679686.26008128</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>19330080.56688496</v>
+        <v>19330080.56090321</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>648.6927830011941</v>
+        <v>648.6927827717927</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>716.0526459700808</v>
+        <v>716.0526468047919</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>777.2888193431031</v>
+        <v>777.2888189009593</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>901.2575624904323</v>
+        <v>901.2575629870674</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>975.6458901271745</v>
+        <v>975.6458898252582</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>648.6927830011941</v>
+        <v>648.6927827717927</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>716.0526459700808</v>
+        <v>716.0526468047919</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>777.2888193431031</v>
+        <v>777.2888189009593</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>901.2575624904323</v>
+        <v>901.2575629870674</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>975.6458901271745</v>
+        <v>975.6458898252582</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>10274389.70005408</v>
+        <v>10274389.69642068</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>12394485.26039501</v>
+        <v>12394485.27484341</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>14400770.13373391</v>
+        <v>14400770.12554235</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>16679686.25088999</v>
+        <v>16679686.26008128</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>19330080.56688496</v>
+        <v>19330080.56090321</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
